--- a/web/cocm-workbook-example.xlsx
+++ b/web/cocm-workbook-example.xlsx
@@ -153,7 +153,7 @@
     <row r="10">
       <c r="A10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">3. Use the same patient id on every tab: a registry number or another id your site assigns, never a name. Keep the workbook at your site.</t>
+          <t xml:space="preserve">3. Use the patient's MRN as the patient id on every tab, never a name, so it matches what the EHR uses. Keep the workbook at your site. To share the tables without MRNs, load your site's pseudonym key on the calculator page first.</t>
         </is>
       </c>
     </row>
